--- a/backend/src/db/demo-docs/measurements-stride-track-jacket.xlsx
+++ b/backend/src/db/demo-docs/measurements-stride-track-jacket.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Poly Spandex Blend</t>
+          <t>88% Polyester 12% Spandex</t>
         </is>
       </c>
     </row>
@@ -653,19 +653,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>71.5</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="F12" s="5" t="n">
         <v>73.5</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="G12" s="5" t="n">
         <v>75.5</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="H12" s="5" t="n">
         <v>77.5</v>
       </c>
     </row>
@@ -746,19 +749,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E15" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="F15" s="5" t="n">
         <v>9.5</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="G15" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="H15" s="5" t="n">
         <v>10.5</v>
       </c>
     </row>
@@ -775,7 +781,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
@@ -785,11 +791,14 @@
         <v>2</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>2.5</v>
       </c>
+      <c r="H16" s="5" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -836,19 +845,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="E18" s="5" t="n">
         <v>79.5</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="F18" s="5" t="n">
         <v>81.5</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="G18" s="5" t="n">
         <v>83.5</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="H18" s="5" t="n">
         <v>85.5</v>
       </c>
     </row>
@@ -929,19 +941,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E21" s="5" t="n">
         <v>33.5</v>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="F21" s="5" t="n">
         <v>34.5</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="G21" s="5" t="n">
         <v>35.5</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="H21" s="5" t="n">
         <v>36.5</v>
       </c>
     </row>
@@ -958,19 +973,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E22" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="F22" s="5" t="n">
         <v>24.5</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="G22" s="5" t="n">
         <v>25.5</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="H22" s="5" t="n">
         <v>26.5</v>
       </c>
     </row>
@@ -987,19 +1005,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="E23" s="5" t="n">
         <v>35.5</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="F23" s="5" t="n">
         <v>36.5</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="G23" s="5" t="n">
         <v>37.5</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="H23" s="5" t="n">
         <v>39</v>
       </c>
     </row>
@@ -1016,19 +1037,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E24" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="F24" s="5" t="n">
         <v>24.5</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="G24" s="5" t="n">
         <v>25.5</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="H24" s="5" t="n">
         <v>26.5</v>
       </c>
     </row>
